--- a/results/data/semih_adaptive_curriculum_dqn_experiment_results.xlsx
+++ b/results/data/semih_adaptive_curriculum_dqn_experiment_results.xlsx
@@ -750,190 +750,190 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>90.8</v>
+        <v>163</v>
       </c>
       <c r="C2" t="n">
-        <v>3.31058907144937</v>
+        <v>13.68210510118966</v>
       </c>
       <c r="D2" t="n">
-        <v>94.8</v>
+        <v>167.7</v>
       </c>
       <c r="E2" t="n">
-        <v>4.894895300208167</v>
+        <v>22.92618590171509</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>166.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.569046515733026</v>
+        <v>15.66397139936102</v>
       </c>
       <c r="H2" t="n">
-        <v>97.7</v>
+        <v>171.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.689173349139344</v>
+        <v>8.161494961096281</v>
       </c>
       <c r="J2" t="n">
-        <v>99.7</v>
+        <v>190.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.73392015141785</v>
+        <v>6.859300255857007</v>
       </c>
       <c r="L2" t="n">
-        <v>100.5</v>
+        <v>192.4</v>
       </c>
       <c r="M2" t="n">
-        <v>4.716990566028302</v>
+        <v>11.0562199688682</v>
       </c>
       <c r="N2" t="n">
-        <v>98.2</v>
+        <v>196</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1559467676119</v>
+        <v>6.356099432828281</v>
       </c>
       <c r="P2" t="n">
-        <v>102.8</v>
+        <v>205.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.62767142944341</v>
+        <v>6.771262806892079</v>
       </c>
       <c r="R2" t="n">
-        <v>102.1</v>
+        <v>206.6</v>
       </c>
       <c r="S2" t="n">
-        <v>5.337602458033007</v>
+        <v>7.631513611335565</v>
       </c>
       <c r="T2" t="n">
-        <v>101.2</v>
+        <v>205.7</v>
       </c>
       <c r="U2" t="n">
-        <v>5.455272678794342</v>
+        <v>7.170076708097342</v>
       </c>
       <c r="V2" t="n">
-        <v>102.7</v>
+        <v>212.2</v>
       </c>
       <c r="W2" t="n">
-        <v>6.694027188471825</v>
+        <v>4.975942121849891</v>
       </c>
       <c r="X2" t="n">
-        <v>105.9</v>
+        <v>217.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.928488612140643</v>
+        <v>9.572878355019455</v>
       </c>
       <c r="Z2" t="n">
-        <v>105.7</v>
+        <v>222.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.337049688440288</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>105.7</v>
+        <v>243</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.148983655857283</v>
+        <v>34.02939905434711</v>
       </c>
       <c r="AD2" t="n">
-        <v>104.7</v>
+        <v>238.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.670117771534247</v>
+        <v>23.12055362658948</v>
       </c>
       <c r="AF2" t="n">
-        <v>104.8</v>
+        <v>302</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.249761899362674</v>
+        <v>55.29195239815646</v>
       </c>
       <c r="AH2" t="n">
-        <v>109.4</v>
+        <v>322</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.977468270071653</v>
+        <v>66.11958862545956</v>
       </c>
       <c r="AJ2" t="n">
-        <v>105.3</v>
+        <v>239.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.74543296888929</v>
+        <v>36.40453268481824</v>
       </c>
       <c r="AL2" t="n">
-        <v>104.2</v>
+        <v>237.6</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.770744176750625</v>
+        <v>38.14498656442286</v>
       </c>
       <c r="AN2" t="n">
-        <v>101.7</v>
+        <v>254.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.243819034784589</v>
+        <v>49.35949756632456</v>
       </c>
       <c r="AP2" t="n">
-        <v>103.9</v>
+        <v>230.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.923681287847955</v>
+        <v>17.38275007011261</v>
       </c>
       <c r="AR2" t="n">
-        <v>107.5</v>
+        <v>224.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.216912416947821</v>
+        <v>7.691553809211763</v>
       </c>
       <c r="AT2" t="n">
-        <v>103.6</v>
+        <v>218.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.462600113499065</v>
+        <v>15.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>114</v>
+        <v>201.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.2469507659596</v>
+        <v>20.90669749147387</v>
       </c>
       <c r="AX2" t="n">
-        <v>112.2</v>
+        <v>200.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.573638491504595</v>
+        <v>23.26821866838972</v>
       </c>
       <c r="AZ2" t="n">
-        <v>108.1</v>
+        <v>178</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.217340230306453</v>
+        <v>12.50599856069079</v>
       </c>
       <c r="BB2" t="n">
-        <v>107.3</v>
+        <v>176.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.391066678319271</v>
+        <v>9.159148432032314</v>
       </c>
       <c r="BD2" t="n">
-        <v>111.4</v>
+        <v>170.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.879189152169246</v>
+        <v>18.16700305498956</v>
       </c>
       <c r="BF2" t="n">
-        <v>113.3</v>
+        <v>168.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.99208072020865</v>
+        <v>22.58406517879365</v>
       </c>
       <c r="BH2" t="n">
-        <v>116.7</v>
+        <v>149.3</v>
       </c>
       <c r="BI2" t="n">
-        <v>13.1533265754333</v>
+        <v>18.90529026489676</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3131.9</v>
+        <v>6273.9</v>
       </c>
       <c r="BK2" t="n">
-        <v>104.3966666666667</v>
+        <v>209.13</v>
       </c>
     </row>
     <row r="3">
@@ -941,190 +941,190 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>93.3</v>
+        <v>159.2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.716180835212409</v>
+        <v>22.03996370232946</v>
       </c>
       <c r="D3" t="n">
-        <v>94.5</v>
+        <v>177.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3.383784863137726</v>
+        <v>21.56293115510969</v>
       </c>
       <c r="F3" t="n">
-        <v>96.40000000000001</v>
+        <v>174.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.104834939252005</v>
+        <v>12.24295715911805</v>
       </c>
       <c r="H3" t="n">
-        <v>98.8</v>
+        <v>189.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.867815921162743</v>
+        <v>19.07773571470157</v>
       </c>
       <c r="J3" t="n">
-        <v>98.7</v>
+        <v>193.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.080354318352216</v>
+        <v>17.16071094098377</v>
       </c>
       <c r="L3" t="n">
-        <v>97.90000000000001</v>
+        <v>194.7</v>
       </c>
       <c r="M3" t="n">
-        <v>5.374941860150676</v>
+        <v>10.38315944209661</v>
       </c>
       <c r="N3" t="n">
-        <v>100</v>
+        <v>192.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4.219004621945797</v>
+        <v>5.44426303552648</v>
       </c>
       <c r="P3" t="n">
-        <v>102.7</v>
+        <v>199.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.017474553332153</v>
+        <v>5.134199061197375</v>
       </c>
       <c r="R3" t="n">
-        <v>99.2</v>
+        <v>202.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.833218389437828</v>
+        <v>6.144916598294887</v>
       </c>
       <c r="T3" t="n">
-        <v>102.9</v>
+        <v>210</v>
       </c>
       <c r="U3" t="n">
-        <v>4.570557952810575</v>
+        <v>7.334848328356899</v>
       </c>
       <c r="V3" t="n">
-        <v>102.2</v>
+        <v>215.2</v>
       </c>
       <c r="W3" t="n">
-        <v>3.709447398198282</v>
+        <v>5.758472019555187</v>
       </c>
       <c r="X3" t="n">
-        <v>103.6</v>
+        <v>215.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.351635264103861</v>
+        <v>5.146843692983109</v>
       </c>
       <c r="Z3" t="n">
-        <v>104.8</v>
+        <v>220.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.762977544445356</v>
+        <v>8.295179322956196</v>
       </c>
       <c r="AB3" t="n">
-        <v>106.3</v>
+        <v>248.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.74299345444258</v>
+        <v>41.21419658321632</v>
       </c>
       <c r="AD3" t="n">
-        <v>107.8</v>
+        <v>258.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.841874542459709</v>
+        <v>43.23840885139045</v>
       </c>
       <c r="AF3" t="n">
-        <v>105.8</v>
+        <v>289.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.114684741017768</v>
+        <v>73.02903532157603</v>
       </c>
       <c r="AH3" t="n">
-        <v>102.4</v>
+        <v>317.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.023942674832188</v>
+        <v>81.71560438496432</v>
       </c>
       <c r="AJ3" t="n">
-        <v>105.5</v>
+        <v>347.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.201190307520001</v>
+        <v>60.74084293126002</v>
       </c>
       <c r="AL3" t="n">
-        <v>106.4</v>
+        <v>281.3</v>
       </c>
       <c r="AM3" t="n">
-        <v>6.974238309665077</v>
+        <v>65.91062129884682</v>
       </c>
       <c r="AN3" t="n">
-        <v>108.5</v>
+        <v>242.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.800735254367722</v>
+        <v>56.42951355452216</v>
       </c>
       <c r="AP3" t="n">
-        <v>109.1</v>
+        <v>227.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.934695379034324</v>
+        <v>19.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>104.8</v>
+        <v>223.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.082372483850309</v>
+        <v>21.78554566679476</v>
       </c>
       <c r="AT3" t="n">
-        <v>107.1</v>
+        <v>227.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.489325737341114</v>
+        <v>22.50866499817348</v>
       </c>
       <c r="AV3" t="n">
-        <v>111.7</v>
+        <v>207.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.60183811107896</v>
+        <v>13.50407345951584</v>
       </c>
       <c r="AX3" t="n">
-        <v>111.6</v>
+        <v>189.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.158212067269313</v>
+        <v>17.95243716045262</v>
       </c>
       <c r="AZ3" t="n">
-        <v>108.4</v>
+        <v>178.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.728309205612248</v>
+        <v>13.44656089860898</v>
       </c>
       <c r="BB3" t="n">
-        <v>106.1</v>
+        <v>172.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.253234063627348</v>
+        <v>8.882004278314666</v>
       </c>
       <c r="BD3" t="n">
-        <v>111.9</v>
+        <v>158.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.016096716428899</v>
+        <v>5.337602458033007</v>
       </c>
       <c r="BF3" t="n">
-        <v>118.1</v>
+        <v>149.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.94529195959647</v>
+        <v>16.27144738491324</v>
       </c>
       <c r="BH3" t="n">
-        <v>116</v>
+        <v>167.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>13.87083270751976</v>
+        <v>28.05779749018087</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3142.5</v>
+        <v>6431.799999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>104.75</v>
+        <v>214.3933333333333</v>
       </c>
     </row>
     <row r="4">
@@ -1132,190 +1132,190 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>88.7</v>
+        <v>190.1</v>
       </c>
       <c r="C4" t="n">
-        <v>19.63186185770468</v>
+        <v>106.0541842644598</v>
       </c>
       <c r="D4" t="n">
-        <v>94.3</v>
+        <v>161.2</v>
       </c>
       <c r="E4" t="n">
-        <v>4.026164427839479</v>
+        <v>13.4892549831338</v>
       </c>
       <c r="F4" t="n">
-        <v>98.7</v>
+        <v>178.9</v>
       </c>
       <c r="G4" t="n">
-        <v>2.368543856465402</v>
+        <v>16.81933411285952</v>
       </c>
       <c r="H4" t="n">
-        <v>97.2</v>
+        <v>189.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.600000000000001</v>
+        <v>20.29187029329726</v>
       </c>
       <c r="J4" t="n">
-        <v>98.5</v>
+        <v>188.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.006245124802026</v>
+        <v>10.35615758860399</v>
       </c>
       <c r="L4" t="n">
-        <v>97.8</v>
+        <v>188.5</v>
       </c>
       <c r="M4" t="n">
-        <v>5.211525688318154</v>
+        <v>11.1915146427997</v>
       </c>
       <c r="N4" t="n">
-        <v>98.90000000000001</v>
+        <v>197.2</v>
       </c>
       <c r="O4" t="n">
-        <v>4.158124577258358</v>
+        <v>5.688585061331157</v>
       </c>
       <c r="P4" t="n">
-        <v>102.5</v>
+        <v>198.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.008321791298265</v>
+        <v>4.904079934095692</v>
       </c>
       <c r="R4" t="n">
-        <v>103.8</v>
+        <v>205.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.749545416973505</v>
+        <v>6.885491994040803</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3</v>
+        <v>206.9</v>
       </c>
       <c r="U4" t="n">
-        <v>3.132091952673165</v>
+        <v>6.80367547726962</v>
       </c>
       <c r="V4" t="n">
-        <v>103.5</v>
+        <v>214.8</v>
       </c>
       <c r="W4" t="n">
-        <v>3.106444913401814</v>
+        <v>5.268775948927797</v>
       </c>
       <c r="X4" t="n">
-        <v>103.6</v>
+        <v>226.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.161395160225577</v>
+        <v>25.25252462626262</v>
       </c>
       <c r="Z4" t="n">
-        <v>104.5</v>
+        <v>230.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.987486951969082</v>
+        <v>30.55830492681163</v>
       </c>
       <c r="AB4" t="n">
-        <v>104.8</v>
+        <v>241.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.237924020083418</v>
+        <v>44.05734898969751</v>
       </c>
       <c r="AD4" t="n">
-        <v>106.6</v>
+        <v>278.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>6.931089380465383</v>
+        <v>63.34421836284666</v>
       </c>
       <c r="AF4" t="n">
-        <v>107.1</v>
+        <v>277.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.889821729050888</v>
+        <v>39.84018072248167</v>
       </c>
       <c r="AH4" t="n">
-        <v>105.2</v>
+        <v>276.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.015974481593781</v>
+        <v>57.84323642397614</v>
       </c>
       <c r="AJ4" t="n">
-        <v>105.7</v>
+        <v>251.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.522782990761708</v>
+        <v>47.19163061391289</v>
       </c>
       <c r="AL4" t="n">
-        <v>104.2</v>
+        <v>237.3</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.749736834815167</v>
+        <v>31.12571284324264</v>
       </c>
       <c r="AN4" t="n">
-        <v>102.3</v>
+        <v>246.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.73392015141785</v>
+        <v>44.10680219648665</v>
       </c>
       <c r="AP4" t="n">
-        <v>108.6</v>
+        <v>231.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.742997197757758</v>
+        <v>18.3850482729853</v>
       </c>
       <c r="AR4" t="n">
-        <v>106.3</v>
+        <v>232.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.798076685952761</v>
+        <v>35.59227444263713</v>
       </c>
       <c r="AT4" t="n">
-        <v>105.8</v>
+        <v>215.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.352245207128441</v>
+        <v>16.07980099379343</v>
       </c>
       <c r="AV4" t="n">
-        <v>112.6</v>
+        <v>219.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.09297316626478</v>
+        <v>14.40867794074113</v>
       </c>
       <c r="AX4" t="n">
-        <v>110.2</v>
+        <v>194.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>13.8260623461635</v>
+        <v>20.16035713969373</v>
       </c>
       <c r="AZ4" t="n">
-        <v>108.1</v>
+        <v>177.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.90506166958867</v>
+        <v>17.32079674841778</v>
       </c>
       <c r="BB4" t="n">
-        <v>107.6</v>
+        <v>175.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.483826030978932</v>
+        <v>11.85959527134042</v>
       </c>
       <c r="BD4" t="n">
-        <v>111.4</v>
+        <v>166.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.74052809715134</v>
+        <v>16.8644596711546</v>
       </c>
       <c r="BF4" t="n">
-        <v>110</v>
+        <v>151.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.929753269845127</v>
+        <v>13.09809146402635</v>
       </c>
       <c r="BH4" t="n">
-        <v>107</v>
+        <v>150.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.228964600958975</v>
+        <v>18.59811818437554</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3117.8</v>
+        <v>6301.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>103.9266666666667</v>
+        <v>210.0566666666667</v>
       </c>
     </row>
     <row r="5">
@@ -1323,190 +1323,190 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>94.2</v>
+        <v>172</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1559467676119</v>
+        <v>15.62049935181331</v>
       </c>
       <c r="D5" t="n">
-        <v>96.2</v>
+        <v>172.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4</v>
+        <v>23.36321895629966</v>
       </c>
       <c r="F5" t="n">
-        <v>96.2</v>
+        <v>171.6</v>
       </c>
       <c r="G5" t="n">
-        <v>3.682390527904394</v>
+        <v>12.29796731171457</v>
       </c>
       <c r="H5" t="n">
-        <v>95.3</v>
+        <v>181</v>
       </c>
       <c r="I5" t="n">
-        <v>4.960846701924985</v>
+        <v>10.18822850156002</v>
       </c>
       <c r="J5" t="n">
-        <v>99.40000000000001</v>
+        <v>188.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.979949748426479</v>
+        <v>11.29822994986383</v>
       </c>
       <c r="L5" t="n">
-        <v>100.3</v>
+        <v>190.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.436568055487916</v>
+        <v>6.086049621881176</v>
       </c>
       <c r="N5" t="n">
-        <v>101.9</v>
+        <v>196.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.78021163428716</v>
+        <v>7.144228439796701</v>
       </c>
       <c r="P5" t="n">
-        <v>101.1</v>
+        <v>206.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.844292530665578</v>
+        <v>6.858571279792899</v>
       </c>
       <c r="R5" t="n">
-        <v>105.3</v>
+        <v>204.3</v>
       </c>
       <c r="S5" t="n">
-        <v>5.139066063011839</v>
+        <v>9.295697929687689</v>
       </c>
       <c r="T5" t="n">
-        <v>105.8</v>
+        <v>207.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.56124969497314</v>
+        <v>2.749545416973504</v>
       </c>
       <c r="V5" t="n">
-        <v>104.5</v>
+        <v>215.1</v>
       </c>
       <c r="W5" t="n">
-        <v>4.4328320518603</v>
+        <v>3.562302626111375</v>
       </c>
       <c r="X5" t="n">
-        <v>104.1</v>
+        <v>217.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.185556864985669</v>
+        <v>4.565084884205331</v>
       </c>
       <c r="Z5" t="n">
-        <v>106.4</v>
+        <v>221.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.079215610874227</v>
+        <v>14.22814112946593</v>
       </c>
       <c r="AB5" t="n">
-        <v>104.2</v>
+        <v>264.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.812483766206386</v>
+        <v>56.01437315546787</v>
       </c>
       <c r="AD5" t="n">
-        <v>106.1</v>
+        <v>257.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>4.7</v>
+        <v>35.25180846424762</v>
       </c>
       <c r="AF5" t="n">
-        <v>104.8</v>
+        <v>279.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.48998886412873</v>
+        <v>41.61778465992634</v>
       </c>
       <c r="AH5" t="n">
-        <v>104.8</v>
+        <v>300.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.044749683231337</v>
+        <v>55.65285257738367</v>
       </c>
       <c r="AJ5" t="n">
-        <v>104.7</v>
+        <v>282.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.754997371187496</v>
+        <v>63.00984050130583</v>
       </c>
       <c r="AL5" t="n">
-        <v>103.3</v>
+        <v>258.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.407345007480164</v>
+        <v>52.6924093205084</v>
       </c>
       <c r="AN5" t="n">
-        <v>105.5</v>
+        <v>238</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.827531841800928</v>
+        <v>24.58861525177862</v>
       </c>
       <c r="AP5" t="n">
-        <v>103.7</v>
+        <v>240.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.694027188471824</v>
+        <v>40.39170706964488</v>
       </c>
       <c r="AR5" t="n">
-        <v>106.3</v>
+        <v>224</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.12965942171799</v>
+        <v>15.7670542588018</v>
       </c>
       <c r="AT5" t="n">
-        <v>104.7</v>
+        <v>207.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.405678154382138</v>
+        <v>13.08587024236447</v>
       </c>
       <c r="AV5" t="n">
-        <v>111.6</v>
+        <v>211.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>10.27813212602368</v>
+        <v>19.41236719207629</v>
       </c>
       <c r="AX5" t="n">
-        <v>105.1</v>
+        <v>195.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.757282683572571</v>
+        <v>23.6323930231367</v>
       </c>
       <c r="AZ5" t="n">
-        <v>104.2</v>
+        <v>171.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.344155686354955</v>
+        <v>7.128113354878695</v>
       </c>
       <c r="BB5" t="n">
-        <v>108.5</v>
+        <v>175.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.34239833544917</v>
+        <v>10.14692071517266</v>
       </c>
       <c r="BD5" t="n">
-        <v>110.8</v>
+        <v>182</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.482924024179399</v>
+        <v>15.23811011904035</v>
       </c>
       <c r="BF5" t="n">
-        <v>110.6</v>
+        <v>146.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.14686274363584</v>
+        <v>13.35514881983724</v>
       </c>
       <c r="BH5" t="n">
-        <v>110.4</v>
+        <v>160</v>
       </c>
       <c r="BI5" t="n">
-        <v>6.248199740725324</v>
+        <v>34.62946722085109</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3120</v>
+        <v>6343.299999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>104</v>
+        <v>211.4433333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1514,190 +1514,190 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>94.90000000000001</v>
+        <v>155.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4.036087214122113</v>
+        <v>25.39763768542264</v>
       </c>
       <c r="D6" t="n">
-        <v>95.5</v>
+        <v>167.1</v>
       </c>
       <c r="E6" t="n">
-        <v>2.156385865284783</v>
+        <v>25.43010027506773</v>
       </c>
       <c r="F6" t="n">
-        <v>98.40000000000001</v>
+        <v>171.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.727636339397171</v>
+        <v>13.18180564262726</v>
       </c>
       <c r="H6" t="n">
-        <v>96</v>
+        <v>182.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.195235392680607</v>
+        <v>18.28141132407452</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>182.1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.234500931320961</v>
+        <v>11.46690891216984</v>
       </c>
       <c r="L6" t="n">
-        <v>97.7</v>
+        <v>193.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.874274125562103</v>
+        <v>9.075241043630742</v>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="O6" t="n">
-        <v>3.492849839314596</v>
+        <v>9.695359714832659</v>
       </c>
       <c r="P6" t="n">
-        <v>102.5</v>
+        <v>200.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.004997502496879</v>
+        <v>4.363484845854286</v>
       </c>
       <c r="R6" t="n">
-        <v>102.5</v>
+        <v>204.3</v>
       </c>
       <c r="S6" t="n">
-        <v>4.631414470763764</v>
+        <v>6.245798587850877</v>
       </c>
       <c r="T6" t="n">
-        <v>102.4</v>
+        <v>210.8</v>
       </c>
       <c r="U6" t="n">
-        <v>3.555277766926235</v>
+        <v>5.564171097297423</v>
       </c>
       <c r="V6" t="n">
-        <v>103.5</v>
+        <v>212.2</v>
       </c>
       <c r="W6" t="n">
-        <v>4.295346318982906</v>
+        <v>10.87933821516732</v>
       </c>
       <c r="X6" t="n">
-        <v>103.8</v>
+        <v>220.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.925747767665559</v>
+        <v>14.77870089013239</v>
       </c>
       <c r="Z6" t="n">
-        <v>105.2</v>
+        <v>231.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.74108003776293</v>
+        <v>19.54712255039089</v>
       </c>
       <c r="AB6" t="n">
-        <v>107.6</v>
+        <v>251.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.019966777316965</v>
+        <v>50.74849751470481</v>
       </c>
       <c r="AD6" t="n">
-        <v>107.1</v>
+        <v>236.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.448187929913334</v>
+        <v>16.43654464904348</v>
       </c>
       <c r="AF6" t="n">
-        <v>106.3</v>
+        <v>270.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.967411499134277</v>
+        <v>47.79790790400768</v>
       </c>
       <c r="AH6" t="n">
-        <v>104.9</v>
+        <v>265.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.614108798023731</v>
+        <v>49.77037271309107</v>
       </c>
       <c r="AJ6" t="n">
-        <v>105</v>
+        <v>238.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.848076606885378</v>
+        <v>30.32556677129053</v>
       </c>
       <c r="AL6" t="n">
-        <v>106.6</v>
+        <v>257.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.103656905736638</v>
+        <v>44.62689771875254</v>
       </c>
       <c r="AN6" t="n">
-        <v>108</v>
+        <v>243.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.889388252060893</v>
+        <v>28.00642783362419</v>
       </c>
       <c r="AP6" t="n">
-        <v>106.5</v>
+        <v>233.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.748912940721924</v>
+        <v>17.63547561025786</v>
       </c>
       <c r="AR6" t="n">
-        <v>105.4</v>
+        <v>225.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.332916650389354</v>
+        <v>16.55173706896047</v>
       </c>
       <c r="AT6" t="n">
-        <v>107</v>
+        <v>218.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.882176467941097</v>
+        <v>24.40819534500656</v>
       </c>
       <c r="AV6" t="n">
-        <v>103.6</v>
+        <v>197.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.238320341483518</v>
+        <v>21.84399230909954</v>
       </c>
       <c r="AX6" t="n">
-        <v>108.9</v>
+        <v>199.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.68289347721702</v>
+        <v>26.7972013464093</v>
       </c>
       <c r="AZ6" t="n">
-        <v>110.1</v>
+        <v>171.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.859458222713169</v>
+        <v>11.51694403911037</v>
       </c>
       <c r="BB6" t="n">
-        <v>110.6</v>
+        <v>169.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.87948125831798</v>
+        <v>14.9545979551441</v>
       </c>
       <c r="BD6" t="n">
-        <v>112.4</v>
+        <v>159.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.42305137663631</v>
+        <v>20.73185954033067</v>
       </c>
       <c r="BF6" t="n">
-        <v>118.2</v>
+        <v>157.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.328265125462805</v>
+        <v>22.99478201679677</v>
       </c>
       <c r="BH6" t="n">
-        <v>110.3</v>
+        <v>151.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>13.72625221974301</v>
+        <v>20.37670238286853</v>
       </c>
       <c r="BJ6" t="n">
-        <v>3143.9</v>
+        <v>6175.600000000002</v>
       </c>
       <c r="BK6" t="n">
-        <v>104.7966666666667</v>
+        <v>205.8533333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1705,190 +1705,190 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>93.8</v>
+        <v>145.8</v>
       </c>
       <c r="C7" t="n">
-        <v>4.6</v>
+        <v>14.00571312000928</v>
       </c>
       <c r="D7" t="n">
-        <v>93.7</v>
+        <v>169.8</v>
       </c>
       <c r="E7" t="n">
-        <v>2.147091055358389</v>
+        <v>19.01473113141493</v>
       </c>
       <c r="F7" t="n">
-        <v>94.90000000000001</v>
+        <v>172</v>
       </c>
       <c r="G7" t="n">
-        <v>4.392038251199549</v>
+        <v>11.48041811085293</v>
       </c>
       <c r="H7" t="n">
-        <v>97.2</v>
+        <v>179.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.762977544445355</v>
+        <v>16.67213243709394</v>
       </c>
       <c r="J7" t="n">
-        <v>99.40000000000001</v>
+        <v>186.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.835489375751565</v>
+        <v>4.887739763939975</v>
       </c>
       <c r="L7" t="n">
-        <v>98.40000000000001</v>
+        <v>190.1</v>
       </c>
       <c r="M7" t="n">
-        <v>4.630334761116091</v>
+        <v>3.806573262134856</v>
       </c>
       <c r="N7" t="n">
-        <v>100.2</v>
+        <v>195.2</v>
       </c>
       <c r="O7" t="n">
-        <v>5.173006862551025</v>
+        <v>6.273754856543249</v>
       </c>
       <c r="P7" t="n">
-        <v>102.1</v>
+        <v>201.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.990826320300064</v>
+        <v>7.691553809211763</v>
       </c>
       <c r="R7" t="n">
-        <v>103.3</v>
+        <v>203.6</v>
       </c>
       <c r="S7" t="n">
-        <v>4.539823785126467</v>
+        <v>6.327716807822551</v>
       </c>
       <c r="T7" t="n">
-        <v>103.5</v>
+        <v>206.5</v>
       </c>
       <c r="U7" t="n">
-        <v>4.318564576337836</v>
+        <v>6.119640512317697</v>
       </c>
       <c r="V7" t="n">
-        <v>103.6</v>
+        <v>210.6</v>
       </c>
       <c r="W7" t="n">
-        <v>4.476605857119878</v>
+        <v>5.370288632839022</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>221.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.847076812334269</v>
+        <v>24.69331893448104</v>
       </c>
       <c r="Z7" t="n">
-        <v>106.6</v>
+        <v>218.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.2</v>
+        <v>8.260750571225351</v>
       </c>
       <c r="AB7" t="n">
-        <v>105.1</v>
+        <v>224.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.323193264243457</v>
+        <v>9.964436762808022</v>
       </c>
       <c r="AD7" t="n">
-        <v>104.1</v>
+        <v>296.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.742362280551751</v>
+        <v>71.18349527804882</v>
       </c>
       <c r="AF7" t="n">
-        <v>107.1</v>
+        <v>273.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.57584074378026</v>
+        <v>47.88621931203172</v>
       </c>
       <c r="AH7" t="n">
-        <v>106.9</v>
+        <v>295.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.935733730830885</v>
+        <v>66.32231901856267</v>
       </c>
       <c r="AJ7" t="n">
-        <v>106.5</v>
+        <v>305.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>6.296824596572466</v>
+        <v>75.4774138401681</v>
       </c>
       <c r="AL7" t="n">
-        <v>104.8</v>
+        <v>264.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>7.011419257183242</v>
+        <v>61.85175826118446</v>
       </c>
       <c r="AN7" t="n">
-        <v>109.5</v>
+        <v>264.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.859300255857007</v>
+        <v>78.88193709589034</v>
       </c>
       <c r="AP7" t="n">
-        <v>108.8</v>
+        <v>239.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.287721626560915</v>
+        <v>42.62640027025505</v>
       </c>
       <c r="AR7" t="n">
-        <v>112.4</v>
+        <v>224</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.17538500417954</v>
+        <v>18.3412104289766</v>
       </c>
       <c r="AT7" t="n">
-        <v>108.4</v>
+        <v>223</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.902173570694959</v>
+        <v>15.27088733505686</v>
       </c>
       <c r="AV7" t="n">
-        <v>103.3</v>
+        <v>212.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.172529209005013</v>
+        <v>20.98189695904543</v>
       </c>
       <c r="AX7" t="n">
-        <v>106.4</v>
+        <v>191.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.774316690230725</v>
+        <v>21.73959521242288</v>
       </c>
       <c r="AZ7" t="n">
-        <v>107.9</v>
+        <v>168.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.717516943569122</v>
+        <v>7.704544113703289</v>
       </c>
       <c r="BB7" t="n">
-        <v>110.2</v>
+        <v>171.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>12.85923792454281</v>
+        <v>12.29471431144295</v>
       </c>
       <c r="BD7" t="n">
-        <v>111.2</v>
+        <v>157</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.829496021857645</v>
+        <v>15.62049935181331</v>
       </c>
       <c r="BF7" t="n">
-        <v>113.3</v>
+        <v>159.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.35825690852254</v>
+        <v>14.29300528230505</v>
       </c>
       <c r="BH7" t="n">
-        <v>115.9</v>
+        <v>162</v>
       </c>
       <c r="BI7" t="n">
-        <v>15.26073392730507</v>
+        <v>29.88645178002902</v>
       </c>
       <c r="BJ7" t="n">
-        <v>3142.5</v>
+        <v>6336</v>
       </c>
       <c r="BK7" t="n">
-        <v>104.75</v>
+        <v>211.2</v>
       </c>
     </row>
     <row r="8">
@@ -1896,190 +1896,190 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>82.40000000000001</v>
+        <v>153.9</v>
       </c>
       <c r="C8" t="n">
-        <v>25.4566297847928</v>
+        <v>15.35219853962292</v>
       </c>
       <c r="D8" t="n">
-        <v>95.40000000000001</v>
+        <v>161.9</v>
       </c>
       <c r="E8" t="n">
-        <v>3.555277766926236</v>
+        <v>14.52205219657332</v>
       </c>
       <c r="F8" t="n">
-        <v>96.40000000000001</v>
+        <v>170.3</v>
       </c>
       <c r="G8" t="n">
-        <v>4.31740662898458</v>
+        <v>17.60142039722931</v>
       </c>
       <c r="H8" t="n">
-        <v>98.40000000000001</v>
+        <v>174.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3.852272056851644</v>
+        <v>8.535221145348256</v>
       </c>
       <c r="J8" t="n">
-        <v>98.2</v>
+        <v>178.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.944616584663204</v>
+        <v>6.726068688320095</v>
       </c>
       <c r="L8" t="n">
-        <v>99.59999999999999</v>
+        <v>189.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.382306905057553</v>
+        <v>9.491575211733824</v>
       </c>
       <c r="N8" t="n">
-        <v>100.2</v>
+        <v>194.7</v>
       </c>
       <c r="O8" t="n">
-        <v>4.48998886412873</v>
+        <v>9.349331526906083</v>
       </c>
       <c r="P8" t="n">
-        <v>103.3</v>
+        <v>202.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.473253849269008</v>
+        <v>7.977468270071652</v>
       </c>
       <c r="R8" t="n">
-        <v>102.7</v>
+        <v>202.9</v>
       </c>
       <c r="S8" t="n">
-        <v>5.197114584074513</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>103.8</v>
+        <v>208.3</v>
       </c>
       <c r="U8" t="n">
-        <v>3.458323293158116</v>
+        <v>7.642643521714199</v>
       </c>
       <c r="V8" t="n">
-        <v>103.4</v>
+        <v>212</v>
       </c>
       <c r="W8" t="n">
-        <v>3.32264954516723</v>
+        <v>5.347896782848375</v>
       </c>
       <c r="X8" t="n">
-        <v>100.6</v>
+        <v>216.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.903060268852505</v>
+        <v>4.924428900898052</v>
       </c>
       <c r="Z8" t="n">
-        <v>101.4</v>
+        <v>234.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.476605857119878</v>
+        <v>34.17542977052374</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.7</v>
+        <v>220.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.817675788178362</v>
+        <v>10.24499877989256</v>
       </c>
       <c r="AD8" t="n">
-        <v>106</v>
+        <v>262.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>5.059644256269407</v>
+        <v>49.88637088424052</v>
       </c>
       <c r="AF8" t="n">
-        <v>108.2</v>
+        <v>261.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.564171097297422</v>
+        <v>47.19629222725023</v>
       </c>
       <c r="AH8" t="n">
-        <v>102.5</v>
+        <v>327</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.153311931459037</v>
+        <v>42.78784874237077</v>
       </c>
       <c r="AJ8" t="n">
-        <v>104.5</v>
+        <v>310.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.80086200490927</v>
+        <v>71.49657334446177</v>
       </c>
       <c r="AL8" t="n">
-        <v>107.7</v>
+        <v>273.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.025584090893323</v>
+        <v>65.49236596734004</v>
       </c>
       <c r="AN8" t="n">
-        <v>109.1</v>
+        <v>247.4</v>
       </c>
       <c r="AO8" t="n">
-        <v>7.133722730804723</v>
+        <v>48.68921851909312</v>
       </c>
       <c r="AP8" t="n">
-        <v>105.4</v>
+        <v>239</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.404760555780278</v>
+        <v>14.51206394693739</v>
       </c>
       <c r="AR8" t="n">
-        <v>108</v>
+        <v>226.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.136338242723197</v>
+        <v>12.14454610102823</v>
       </c>
       <c r="AT8" t="n">
-        <v>108</v>
+        <v>215.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>10.58300524425836</v>
+        <v>10.53755189785559</v>
       </c>
       <c r="AV8" t="n">
-        <v>109.1</v>
+        <v>201.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.159148432032314</v>
+        <v>15.36261696456694</v>
       </c>
       <c r="AX8" t="n">
-        <v>112.2</v>
+        <v>185</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.713907555664713</v>
+        <v>20.62037827005121</v>
       </c>
       <c r="AZ8" t="n">
-        <v>113.7</v>
+        <v>178.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.1988635874457</v>
+        <v>9.335952013587045</v>
       </c>
       <c r="BB8" t="n">
-        <v>107.8</v>
+        <v>176.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>10.34214677907832</v>
+        <v>10.85172797300043</v>
       </c>
       <c r="BD8" t="n">
-        <v>110.5</v>
+        <v>175.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.003570517957251</v>
+        <v>12.91859125446734</v>
       </c>
       <c r="BF8" t="n">
-        <v>111.6</v>
+        <v>145.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>15.54477404145844</v>
+        <v>7.798076685952761</v>
       </c>
       <c r="BH8" t="n">
-        <v>108.4</v>
+        <v>149</v>
       </c>
       <c r="BI8" t="n">
-        <v>11.65504182746677</v>
+        <v>16.74514855114758</v>
       </c>
       <c r="BJ8" t="n">
-        <v>3125.2</v>
+        <v>6295</v>
       </c>
       <c r="BK8" t="n">
-        <v>104.1733333333333</v>
+        <v>209.8333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -2087,190 +2087,190 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>83.40000000000001</v>
+        <v>166.7</v>
       </c>
       <c r="C9" t="n">
-        <v>25.22379828653884</v>
+        <v>19.85975830668641</v>
       </c>
       <c r="D9" t="n">
-        <v>97.5</v>
+        <v>164.7</v>
       </c>
       <c r="E9" t="n">
-        <v>2.61725046566048</v>
+        <v>12.05031119930104</v>
       </c>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>176.8</v>
       </c>
       <c r="G9" t="n">
-        <v>4.09878030638384</v>
+        <v>12.37578280352399</v>
       </c>
       <c r="H9" t="n">
-        <v>96.7</v>
+        <v>170.4</v>
       </c>
       <c r="I9" t="n">
-        <v>3.661966684720111</v>
+        <v>14.06556077801379</v>
       </c>
       <c r="J9" t="n">
-        <v>99.90000000000001</v>
+        <v>188.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.385372088375313</v>
+        <v>13.36600164596728</v>
       </c>
       <c r="L9" t="n">
-        <v>100.8</v>
+        <v>189.3</v>
       </c>
       <c r="M9" t="n">
-        <v>5.635601121442148</v>
+        <v>10.53612832116238</v>
       </c>
       <c r="N9" t="n">
-        <v>98.5</v>
+        <v>196.2</v>
       </c>
       <c r="O9" t="n">
-        <v>5.714017850864661</v>
+        <v>8.6</v>
       </c>
       <c r="P9" t="n">
-        <v>101</v>
+        <v>200.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6475800154489</v>
+        <v>8.124653838779841</v>
       </c>
       <c r="R9" t="n">
-        <v>100.5</v>
+        <v>205.2</v>
       </c>
       <c r="S9" t="n">
-        <v>4.964876634922564</v>
+        <v>7.997499609252881</v>
       </c>
       <c r="T9" t="n">
-        <v>106.2</v>
+        <v>209</v>
       </c>
       <c r="U9" t="n">
-        <v>4.142463035441596</v>
+        <v>4.123105625617661</v>
       </c>
       <c r="V9" t="n">
-        <v>102.6</v>
+        <v>211.9</v>
       </c>
       <c r="W9" t="n">
-        <v>4.903060268852505</v>
+        <v>5.769748694700663</v>
       </c>
       <c r="X9" t="n">
-        <v>104.2</v>
+        <v>218.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.582114294781145</v>
+        <v>6.885491994040803</v>
       </c>
       <c r="Z9" t="n">
-        <v>103</v>
+        <v>241.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.669047011971501</v>
+        <v>39.20918259795784</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.6</v>
+        <v>243.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.82078831727758</v>
+        <v>37.76625477857183</v>
       </c>
       <c r="AD9" t="n">
-        <v>106.7</v>
+        <v>249.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.925557285278104</v>
+        <v>26.99703687444235</v>
       </c>
       <c r="AF9" t="n">
-        <v>103.1</v>
+        <v>274.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.146843692983108</v>
+        <v>58.93462479731249</v>
       </c>
       <c r="AH9" t="n">
-        <v>106.2</v>
+        <v>273.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.939740629158989</v>
+        <v>67.33023095163124</v>
       </c>
       <c r="AJ9" t="n">
-        <v>104.3</v>
+        <v>297.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.377869150810907</v>
+        <v>72.15545717407659</v>
       </c>
       <c r="AL9" t="n">
-        <v>103.4</v>
+        <v>264.4</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.8</v>
+        <v>70.17150418795367</v>
       </c>
       <c r="AN9" t="n">
-        <v>103</v>
+        <v>266.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>3.847076812334269</v>
+        <v>64.25612811242209</v>
       </c>
       <c r="AP9" t="n">
-        <v>107.3</v>
+        <v>249.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.668767828015137</v>
+        <v>34.64736642228382</v>
       </c>
       <c r="AR9" t="n">
-        <v>108.8</v>
+        <v>234</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.761278445523805</v>
+        <v>26.14956978613606</v>
       </c>
       <c r="AT9" t="n">
-        <v>112.7</v>
+        <v>216.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.119570294468081</v>
+        <v>15.98280325850256</v>
       </c>
       <c r="AV9" t="n">
-        <v>108.5</v>
+        <v>211.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.163945124754331</v>
+        <v>26.62874386823381</v>
       </c>
       <c r="AX9" t="n">
-        <v>113</v>
+        <v>192.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.57355191030904</v>
+        <v>19.331063085097</v>
       </c>
       <c r="AZ9" t="n">
-        <v>109.4</v>
+        <v>178.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.057593499379401</v>
+        <v>15.18189711465599</v>
       </c>
       <c r="BB9" t="n">
-        <v>108.2</v>
+        <v>172</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.453041838477178</v>
+        <v>11.48041811085293</v>
       </c>
       <c r="BD9" t="n">
-        <v>117.8</v>
+        <v>156.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.44748483277715</v>
+        <v>14.10141836837699</v>
       </c>
       <c r="BF9" t="n">
-        <v>109.4</v>
+        <v>162.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.871170143402454</v>
+        <v>39.02678567343204</v>
       </c>
       <c r="BH9" t="n">
-        <v>109.2</v>
+        <v>151.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>12.85145906113388</v>
+        <v>16.46845469374707</v>
       </c>
       <c r="BJ9" t="n">
-        <v>3124.9</v>
+        <v>6332.000000000002</v>
       </c>
       <c r="BK9" t="n">
-        <v>104.1633333333333</v>
+        <v>211.0666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -2278,190 +2278,190 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>93.3</v>
+        <v>153.9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.436568055487916</v>
+        <v>23.44546864534808</v>
       </c>
       <c r="D10" t="n">
-        <v>88.5</v>
+        <v>182.7</v>
       </c>
       <c r="E10" t="n">
-        <v>21.13882683594338</v>
+        <v>23.71096792625725</v>
       </c>
       <c r="F10" t="n">
-        <v>96.3</v>
+        <v>181.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.382921400162226</v>
+        <v>16.32298992219256</v>
       </c>
       <c r="H10" t="n">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="I10" t="n">
-        <v>3.54964786985977</v>
+        <v>10.16857905510893</v>
       </c>
       <c r="J10" t="n">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="K10" t="n">
-        <v>4.219004621945797</v>
+        <v>11.69615321377076</v>
       </c>
       <c r="L10" t="n">
-        <v>99.59999999999999</v>
+        <v>190.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.720215047547655</v>
+        <v>7.459222479588607</v>
       </c>
       <c r="N10" t="n">
-        <v>101.6</v>
+        <v>196.1</v>
       </c>
       <c r="O10" t="n">
-        <v>6.069596362197408</v>
+        <v>4.548626166217664</v>
       </c>
       <c r="P10" t="n">
-        <v>102</v>
+        <v>198.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.687817782917155</v>
+        <v>5.509990925582364</v>
       </c>
       <c r="R10" t="n">
-        <v>99.59999999999999</v>
+        <v>204.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.238320341483519</v>
+        <v>6.446704584514479</v>
       </c>
       <c r="T10" t="n">
-        <v>102.4</v>
+        <v>212.2</v>
       </c>
       <c r="U10" t="n">
-        <v>5.607138307550475</v>
+        <v>6.779380502671317</v>
       </c>
       <c r="V10" t="n">
-        <v>102.4</v>
+        <v>210.8</v>
       </c>
       <c r="W10" t="n">
-        <v>3.583294573433783</v>
+        <v>7.586830695356262</v>
       </c>
       <c r="X10" t="n">
-        <v>101.7</v>
+        <v>228.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.879549159502341</v>
+        <v>24.25716389028198</v>
       </c>
       <c r="Z10" t="n">
-        <v>104.9</v>
+        <v>219</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.68242905807015</v>
+        <v>8.087026647662292</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.3</v>
+        <v>275</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.220189569201838</v>
+        <v>46.65190242637485</v>
       </c>
       <c r="AD10" t="n">
-        <v>104.6</v>
+        <v>259.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>6.945502141674136</v>
+        <v>38.83503572806391</v>
       </c>
       <c r="AF10" t="n">
-        <v>105.3</v>
+        <v>296.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.257299494980467</v>
+        <v>58.00077585687971</v>
       </c>
       <c r="AH10" t="n">
-        <v>105.7</v>
+        <v>246.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.848376280978771</v>
+        <v>35.42103894580169</v>
       </c>
       <c r="AJ10" t="n">
-        <v>106.9</v>
+        <v>282.8</v>
       </c>
       <c r="AK10" t="n">
-        <v>6.187891401761992</v>
+        <v>78.26084589371622</v>
       </c>
       <c r="AL10" t="n">
-        <v>103.7</v>
+        <v>271.1</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.465544690232691</v>
+        <v>61.6529804632347</v>
       </c>
       <c r="AN10" t="n">
-        <v>108.1</v>
+        <v>242.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>6.363175307973213</v>
+        <v>48.77130303774956</v>
       </c>
       <c r="AP10" t="n">
-        <v>110.6</v>
+        <v>244</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.073895673530958</v>
+        <v>33.8673884437522</v>
       </c>
       <c r="AR10" t="n">
-        <v>107</v>
+        <v>232.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.276941930590086</v>
+        <v>15.65758602083987</v>
       </c>
       <c r="AT10" t="n">
-        <v>107.1</v>
+        <v>219.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.676981041814026</v>
+        <v>21.8268183664042</v>
       </c>
       <c r="AV10" t="n">
-        <v>113</v>
+        <v>210.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.38419957660617</v>
+        <v>23.41815535006974</v>
       </c>
       <c r="AX10" t="n">
-        <v>105.1</v>
+        <v>196.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.080584360149873</v>
+        <v>18.26061335223984</v>
       </c>
       <c r="AZ10" t="n">
-        <v>111</v>
+        <v>174.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.618156843109719</v>
+        <v>5.817215828899596</v>
       </c>
       <c r="BB10" t="n">
-        <v>110.7</v>
+        <v>175.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>12.21515452214994</v>
+        <v>11.20892501536164</v>
       </c>
       <c r="BD10" t="n">
-        <v>106.7</v>
+        <v>162</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.579627031520658</v>
+        <v>10.28591269649903</v>
       </c>
       <c r="BF10" t="n">
-        <v>117.8</v>
+        <v>143.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.41921302210488</v>
+        <v>11.8928549978548</v>
       </c>
       <c r="BH10" t="n">
-        <v>119.9</v>
+        <v>162</v>
       </c>
       <c r="BI10" t="n">
-        <v>14.27900556761569</v>
+        <v>27.51726730618431</v>
       </c>
       <c r="BJ10" t="n">
-        <v>3141.8</v>
+        <v>6332.2</v>
       </c>
       <c r="BK10" t="n">
-        <v>104.7266666666667</v>
+        <v>211.0733333333333</v>
       </c>
     </row>
     <row r="11">
@@ -2469,190 +2469,190 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>96.09999999999999</v>
+        <v>148.8</v>
       </c>
       <c r="C11" t="n">
-        <v>2.343074902771996</v>
+        <v>10.50523678933512</v>
       </c>
       <c r="D11" t="n">
-        <v>97.09999999999999</v>
+        <v>156.8</v>
       </c>
       <c r="E11" t="n">
-        <v>3.477067730142742</v>
+        <v>13.05986217385161</v>
       </c>
       <c r="F11" t="n">
-        <v>94.59999999999999</v>
+        <v>174.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.608687448721165</v>
+        <v>17.0598944897089</v>
       </c>
       <c r="H11" t="n">
-        <v>98.2</v>
+        <v>183.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.515679166249389</v>
+        <v>24.27426620930074</v>
       </c>
       <c r="J11" t="n">
-        <v>99.2</v>
+        <v>189.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.458323293158117</v>
+        <v>6.305553108173778</v>
       </c>
       <c r="L11" t="n">
-        <v>98.3</v>
+        <v>187.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.382921400162226</v>
+        <v>9.100000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>105.2</v>
+        <v>199.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.481934729198171</v>
+        <v>6.591661399070799</v>
       </c>
       <c r="P11" t="n">
-        <v>103.4</v>
+        <v>197.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.63868107973205</v>
+        <v>6.905794668247818</v>
       </c>
       <c r="R11" t="n">
-        <v>105.7</v>
+        <v>205.4</v>
       </c>
       <c r="S11" t="n">
-        <v>4.405678154382138</v>
+        <v>8.357032966310472</v>
       </c>
       <c r="T11" t="n">
-        <v>105.1</v>
+        <v>205.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.66270539113887</v>
+        <v>6.466065264130885</v>
       </c>
       <c r="V11" t="n">
-        <v>104.7</v>
+        <v>213.1</v>
       </c>
       <c r="W11" t="n">
-        <v>5.1</v>
+        <v>7.286288492778748</v>
       </c>
       <c r="X11" t="n">
-        <v>102.6</v>
+        <v>218</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.31740662898458</v>
+        <v>6.244997998398398</v>
       </c>
       <c r="Z11" t="n">
-        <v>105.4</v>
+        <v>228.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.063595560468865</v>
+        <v>31.64869665562865</v>
       </c>
       <c r="AB11" t="n">
-        <v>104</v>
+        <v>264.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.242640687119285</v>
+        <v>50.59733194546922</v>
       </c>
       <c r="AD11" t="n">
-        <v>103.9</v>
+        <v>260.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.742362280551751</v>
+        <v>44.45177161823812</v>
       </c>
       <c r="AF11" t="n">
-        <v>107.1</v>
+        <v>304.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.614108798023731</v>
+        <v>57.57786032842832</v>
       </c>
       <c r="AH11" t="n">
-        <v>106.9</v>
+        <v>337.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.374941860150676</v>
+        <v>52.0522814101361</v>
       </c>
       <c r="AJ11" t="n">
-        <v>105</v>
+        <v>318.6</v>
       </c>
       <c r="AK11" t="n">
-        <v>5.89915248150105</v>
+        <v>70.73217089839672</v>
       </c>
       <c r="AL11" t="n">
-        <v>106.2</v>
+        <v>252</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.044749683231337</v>
+        <v>46.50161287525412</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.8</v>
+        <v>233.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.912698199637793</v>
+        <v>43.54365625438452</v>
       </c>
       <c r="AP11" t="n">
-        <v>106.4</v>
+        <v>237.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.086049621881176</v>
+        <v>15.19901312585788</v>
       </c>
       <c r="AR11" t="n">
-        <v>106.1</v>
+        <v>227.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.685057965343307</v>
+        <v>14.16192077368038</v>
       </c>
       <c r="AT11" t="n">
-        <v>104.2</v>
+        <v>221.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.446704584514478</v>
+        <v>18.03995565404749</v>
       </c>
       <c r="AV11" t="n">
-        <v>110.1</v>
+        <v>204.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.76522178127325</v>
+        <v>15.71146078504478</v>
       </c>
       <c r="AX11" t="n">
-        <v>106.1</v>
+        <v>192.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.09405765784999</v>
+        <v>20.16655647352815</v>
       </c>
       <c r="AZ11" t="n">
-        <v>110.8</v>
+        <v>178.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.43117407632541</v>
+        <v>10.04041831797859</v>
       </c>
       <c r="BB11" t="n">
-        <v>111.3</v>
+        <v>177</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.210359310042405</v>
+        <v>12.32882800593795</v>
       </c>
       <c r="BD11" t="n">
-        <v>106.3</v>
+        <v>163.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.18972743189038</v>
+        <v>24.6973682808513</v>
       </c>
       <c r="BF11" t="n">
-        <v>119.2</v>
+        <v>161.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.65137355726522</v>
+        <v>23.83044271514904</v>
       </c>
       <c r="BH11" t="n">
-        <v>111.5</v>
+        <v>154.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>9.531526635329726</v>
+        <v>23.54060322081828</v>
       </c>
       <c r="BJ11" t="n">
-        <v>3146.5</v>
+        <v>6395.099999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>104.8833333333333</v>
+        <v>213.17</v>
       </c>
     </row>
   </sheetData>
